--- a/output/reporte_limpieza.xlsx
+++ b/output/reporte_limpieza.xlsx
@@ -497,7 +497,7 @@
         <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
         <v>76</v>
@@ -537,7 +537,7 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
         <v>200</v>
@@ -577,7 +577,7 @@
         <v>240</v>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
         <v>239</v>
@@ -617,7 +617,7 @@
         <v>119</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
         <v>119</v>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PEIP.xlsx</t>
+          <t>PEIP_solomant.xlsx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -657,7 +657,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
         <v>23</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -697,7 +697,7 @@
         <v>136</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>136</v>
@@ -737,7 +737,7 @@
         <v>54856</v>
       </c>
       <c r="G8" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H8" t="n">
         <v>54856</v>
@@ -777,7 +777,7 @@
         <v>55014</v>
       </c>
       <c r="G9" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H9" t="n">
         <v>55014</v>
@@ -817,7 +817,7 @@
         <v>172</v>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
         <v>172</v>
@@ -857,7 +857,7 @@
         <v>417</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
         <v>417</v>
@@ -897,7 +897,7 @@
         <v>1585</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H12" t="n">
         <v>1585</v>
@@ -937,7 +937,7 @@
         <v>116</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
         <v>116</v>
@@ -977,7 +977,7 @@
         <v>180</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
         <v>180</v>
@@ -1017,7 +1017,7 @@
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H15" t="n">
         <v>60</v>
@@ -1057,7 +1057,7 @@
         <v>517</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
         <v>517</v>
@@ -1097,7 +1097,7 @@
         <v>418</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H17" t="n">
         <v>418</v>
@@ -1137,7 +1137,7 @@
         <v>330</v>
       </c>
       <c r="G18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H18" t="n">
         <v>329</v>
@@ -1177,7 +1177,7 @@
         <v>7390</v>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
         <v>7241</v>
@@ -1217,7 +1217,7 @@
         <v>651</v>
       </c>
       <c r="G20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H21" t="n">
         <v>40</v>
@@ -1297,7 +1297,7 @@
         <v>158</v>
       </c>
       <c r="G22" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H22" t="n">
         <v>155</v>
@@ -1337,7 +1337,7 @@
         <v>17684</v>
       </c>
       <c r="G23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H23" t="n">
         <v>17684</v>
@@ -1377,7 +1377,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H24" t="n">
         <v>64</v>
@@ -1417,7 +1417,7 @@
         <v>278</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
         <v>278</v>
@@ -1457,7 +1457,7 @@
         <v>2036</v>
       </c>
       <c r="G26" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H26" t="n">
         <v>2035</v>
@@ -1497,7 +1497,7 @@
         <v>2035</v>
       </c>
       <c r="G27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H27" t="n">
         <v>2035</v>
@@ -1537,7 +1537,7 @@
         <v>2035</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H28" t="n">
         <v>2035</v>
@@ -1577,7 +1577,7 @@
         <v>2035</v>
       </c>
       <c r="G29" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H29" t="n">
         <v>2035</v>
@@ -1617,7 +1617,7 @@
         <v>121</v>
       </c>
       <c r="G30" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H30" t="n">
         <v>121</v>
@@ -1657,7 +1657,7 @@
         <v>206</v>
       </c>
       <c r="G31" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H31" t="n">
         <v>206</v>
@@ -1697,7 +1697,7 @@
         <v>404</v>
       </c>
       <c r="G32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H32" t="n">
         <v>403</v>
@@ -1737,7 +1737,7 @@
         <v>126</v>
       </c>
       <c r="G33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
         <v>126</v>
@@ -1777,7 +1777,7 @@
         <v>410</v>
       </c>
       <c r="G34" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H34" t="n">
         <v>410</v>

--- a/output/reporte_limpieza.xlsx
+++ b/output/reporte_limpieza.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
         <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
         <v>76</v>
@@ -537,7 +537,7 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
         <v>200</v>
@@ -546,7 +546,7 @@
         <v>200</v>
       </c>
       <c r="J3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -577,16 +577,16 @@
         <v>240</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I4" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J4" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5">
@@ -617,7 +617,7 @@
         <v>119</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
         <v>119</v>
@@ -657,7 +657,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
         <v>23</v>
@@ -697,7 +697,7 @@
         <v>136</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
         <v>136</v>
@@ -737,7 +737,7 @@
         <v>54856</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H8" t="n">
         <v>54856</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>54655</v>
+        <v>54762</v>
       </c>
     </row>
     <row r="9">
@@ -777,7 +777,7 @@
         <v>55014</v>
       </c>
       <c r="G9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9" t="n">
         <v>55014</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>54947</v>
+        <v>54973</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         <v>172</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" t="n">
         <v>172</v>
@@ -857,7 +857,7 @@
         <v>417</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
         <v>417</v>
@@ -897,7 +897,7 @@
         <v>1585</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12" t="n">
         <v>1585</v>
@@ -937,7 +937,7 @@
         <v>116</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
         <v>116</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -977,7 +977,7 @@
         <v>180</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
         <v>180</v>
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -1017,7 +1017,7 @@
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" t="n">
         <v>60</v>
@@ -1057,7 +1057,7 @@
         <v>517</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H16" t="n">
         <v>517</v>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1097,7 @@
         <v>418</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
         <v>418</v>
@@ -1137,7 +1137,7 @@
         <v>330</v>
       </c>
       <c r="G18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H18" t="n">
         <v>329</v>
@@ -1146,7 +1146,7 @@
         <v>329</v>
       </c>
       <c r="J18" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19">
@@ -1177,7 +1177,7 @@
         <v>7390</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" t="n">
         <v>7241</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7104</v>
+        <v>7111</v>
       </c>
     </row>
     <row r="20">
@@ -1217,7 +1217,7 @@
         <v>651</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" t="n">
         <v>40</v>
@@ -1266,7 +1266,7 @@
         <v>40</v>
       </c>
       <c r="J21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -1297,7 +1297,7 @@
         <v>158</v>
       </c>
       <c r="G22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H22" t="n">
         <v>155</v>
@@ -1306,7 +1306,7 @@
         <v>155</v>
       </c>
       <c r="J22" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23">
@@ -1337,7 +1337,7 @@
         <v>17684</v>
       </c>
       <c r="G23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H23" t="n">
         <v>17684</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>17410</v>
+        <v>17616</v>
       </c>
     </row>
     <row r="24">
@@ -1377,16 +1377,16 @@
         <v>77</v>
       </c>
       <c r="G24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -1417,7 +1417,7 @@
         <v>278</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
         <v>278</v>
@@ -1426,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26">
@@ -1457,7 +1457,7 @@
         <v>2036</v>
       </c>
       <c r="G26" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H26" t="n">
         <v>2035</v>
@@ -1497,7 +1497,7 @@
         <v>2035</v>
       </c>
       <c r="G27" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H27" t="n">
         <v>2035</v>
@@ -1537,7 +1537,7 @@
         <v>2035</v>
       </c>
       <c r="G28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" t="n">
         <v>2035</v>
@@ -1577,7 +1577,7 @@
         <v>2035</v>
       </c>
       <c r="G29" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H29" t="n">
         <v>2035</v>
@@ -1617,7 +1617,7 @@
         <v>121</v>
       </c>
       <c r="G30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H30" t="n">
         <v>121</v>
@@ -1657,7 +1657,7 @@
         <v>206</v>
       </c>
       <c r="G31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H31" t="n">
         <v>206</v>
@@ -1697,7 +1697,7 @@
         <v>404</v>
       </c>
       <c r="G32" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H32" t="n">
         <v>403</v>
@@ -1737,7 +1737,7 @@
         <v>126</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H33" t="n">
         <v>126</v>
@@ -1777,7 +1777,7 @@
         <v>410</v>
       </c>
       <c r="G34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H34" t="n">
         <v>410</v>
@@ -1787,6 +1787,46 @@
       </c>
       <c r="J34" t="n">
         <v>409</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>df_pi_listados_final_v7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>df_pi_listados_final_v7.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>con_cod_local</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>186974</v>
+      </c>
+      <c r="G35" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" t="n">
+        <v>186974</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>186783</v>
       </c>
     </row>
   </sheetData>
@@ -1800,7 +1840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1843,143 +1883,159 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3565</v>
+        <v>186974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MODULOS</t>
+          <t>PI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>718</v>
+        <v>3565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ACONDICIONAMIENTO</t>
+          <t>MODULOS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1069</v>
+        <v>718</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASISTENCIAS-SIMILAR</t>
+          <t>ACONDICIONAMIENTO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>112890</v>
+        <v>1069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO</t>
+          <t>ASISTENCIAS-SIMILAR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>2193</v>
+        <v>112890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SANEAMIENTO</t>
+          <t>MANTENIMIENTO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>17684</v>
+        <v>2193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PROGRAMAS PRESUPUESTALES</t>
+          <t>SANEAMIENTO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>2112</v>
+        <v>17684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>PROGRAMAS PRESUPUESTALES</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>7720</v>
+        <v>2112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>INSPECCIONES</t>
+          <t>OTROS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7720</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>INSPECCIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C12" t="n">
         <v>126</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>DEMOLICIONES</t>
         </is>

--- a/output/reporte_limpieza.xlsx
+++ b/output/reporte_limpieza.xlsx
@@ -497,7 +497,7 @@
         <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
         <v>76</v>
@@ -537,7 +537,7 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
         <v>200</v>
@@ -577,7 +577,7 @@
         <v>240</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
         <v>240</v>
@@ -617,7 +617,7 @@
         <v>119</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
         <v>119</v>
@@ -657,7 +657,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
         <v>23</v>
@@ -697,7 +697,7 @@
         <v>136</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
         <v>136</v>
@@ -737,7 +737,7 @@
         <v>54856</v>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H8" t="n">
         <v>54856</v>
@@ -777,7 +777,7 @@
         <v>55014</v>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H9" t="n">
         <v>55014</v>
@@ -817,7 +817,7 @@
         <v>172</v>
       </c>
       <c r="G10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H10" t="n">
         <v>172</v>
@@ -857,7 +857,7 @@
         <v>417</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
         <v>417</v>
@@ -897,7 +897,7 @@
         <v>1585</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H12" t="n">
         <v>1585</v>
@@ -937,7 +937,7 @@
         <v>116</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H13" t="n">
         <v>116</v>
@@ -977,7 +977,7 @@
         <v>180</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H14" t="n">
         <v>180</v>
@@ -1017,7 +1017,7 @@
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H15" t="n">
         <v>60</v>
@@ -1057,7 +1057,7 @@
         <v>517</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
         <v>517</v>
@@ -1097,7 +1097,7 @@
         <v>418</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
         <v>418</v>
@@ -1137,7 +1137,7 @@
         <v>330</v>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H18" t="n">
         <v>329</v>
@@ -1177,7 +1177,7 @@
         <v>7390</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H19" t="n">
         <v>7241</v>
@@ -1217,7 +1217,7 @@
         <v>651</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H21" t="n">
         <v>40</v>
@@ -1297,7 +1297,7 @@
         <v>158</v>
       </c>
       <c r="G22" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H22" t="n">
         <v>155</v>
@@ -1337,7 +1337,7 @@
         <v>17684</v>
       </c>
       <c r="G23" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H23" t="n">
         <v>17684</v>
@@ -1377,7 +1377,7 @@
         <v>77</v>
       </c>
       <c r="G24" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H24" t="n">
         <v>65</v>
@@ -1417,7 +1417,7 @@
         <v>278</v>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H25" t="n">
         <v>278</v>
@@ -1457,7 +1457,7 @@
         <v>2036</v>
       </c>
       <c r="G26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H26" t="n">
         <v>2035</v>
@@ -1497,7 +1497,7 @@
         <v>2035</v>
       </c>
       <c r="G27" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H27" t="n">
         <v>2035</v>
@@ -1537,7 +1537,7 @@
         <v>2035</v>
       </c>
       <c r="G28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H28" t="n">
         <v>2035</v>
@@ -1577,7 +1577,7 @@
         <v>2035</v>
       </c>
       <c r="G29" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H29" t="n">
         <v>2035</v>
@@ -1617,7 +1617,7 @@
         <v>121</v>
       </c>
       <c r="G30" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H30" t="n">
         <v>121</v>
@@ -1657,7 +1657,7 @@
         <v>206</v>
       </c>
       <c r="G31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H31" t="n">
         <v>206</v>
@@ -1697,7 +1697,7 @@
         <v>404</v>
       </c>
       <c r="G32" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H32" t="n">
         <v>403</v>
@@ -1737,7 +1737,7 @@
         <v>126</v>
       </c>
       <c r="G33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H33" t="n">
         <v>126</v>
@@ -1777,7 +1777,7 @@
         <v>410</v>
       </c>
       <c r="G34" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H34" t="n">
         <v>410</v>
@@ -1817,7 +1817,7 @@
         <v>186974</v>
       </c>
       <c r="G35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H35" t="n">
         <v>186974</v>

--- a/output/reporte_limpieza.xlsx
+++ b/output/reporte_limpieza.xlsx
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>54762</v>
+        <v>54802</v>
       </c>
     </row>
     <row r="9">
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>54973</v>
+        <v>55014</v>
       </c>
     </row>
     <row r="10">
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12">
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1579</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="13">
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="17">
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7111</v>
+        <v>7112</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>17616</v>
+        <v>17630</v>
       </c>
     </row>
     <row r="24">
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>186783</v>
+        <v>186942</v>
       </c>
     </row>
   </sheetData>
